--- a/output/勤務変更管理システム.xlsx
+++ b/output/勤務変更管理システム.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +116,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1417,7 +1420,7 @@
           <t>パスワード</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1425,7 +1428,7 @@
           <t>対象日</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
+      <c r="B5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1433,7 +1436,7 @@
           <t>現在の勤務(自動表示)</t>
         </is>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <f>IFERROR(INDEX(シフト表!$B$5:$AF$200,MATCH($B$3,シフト表!$A$5:$A$200,0),MATCH(DAY($B$5),シフト表!$B$3:$AF$3,0)),"-")</f>
         <v/>
       </c>
@@ -1524,7 +1527,7 @@
           <t>パスワード</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
+      <c r="B5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1654,7 +1657,7 @@
           <t>パスワード</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
+      <c r="B5" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1747,7 +1750,7 @@
           <t>パスワード</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1763,7 +1766,7 @@
           <t>対象日A</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
+      <c r="B7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1771,7 +1774,7 @@
           <t>現在の勤務A(自動表示)</t>
         </is>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <f>IFERROR(INDEX(シフト表!$B$5:$AF$200,MATCH($B$7,シフト表!$A$5:$A$200,0),MATCH(DAY($B$8),シフト表!$B$3:$AF$3,0)),"-")</f>
         <v/>
       </c>
@@ -1798,7 +1801,7 @@
           <t>対象日B</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
+      <c r="B12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1806,7 +1809,7 @@
           <t>現在の勤務B(自動表示)</t>
         </is>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="10">
         <f>IFERROR(INDEX(シフト表!$B$5:$AF$200,MATCH($B$12,シフト表!$A$5:$A$200,0),MATCH(DAY($B$13),シフト表!$B$3:$AF$3,0)),"-")</f>
         <v/>
       </c>
@@ -4002,7 +4005,7 @@
           <t>対象年月初日</t>
         </is>
       </c>
-      <c r="B1" s="10" t="n">
+      <c r="B1" s="11" t="n">
         <v>46235</v>
       </c>
     </row>

--- a/output/勤務変更管理システム.xlsx
+++ b/output/勤務変更管理システム.xlsx
@@ -12,12 +12,14 @@
     <sheet name="承認" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ロールバック" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="交換申請" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="履歴" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="職員マスタ" sheetId="7" state="veryHidden" r:id="rId7"/>
-    <sheet name="設定" sheetId="8" state="veryHidden" r:id="rId8"/>
+    <sheet name="有給申請" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="超過勤務申請" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="履歴" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="職員マスタ" sheetId="9" state="veryHidden" r:id="rId9"/>
+    <sheet name="設定" sheetId="10" state="veryHidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'履歴'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'履歴'!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,9 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -103,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,6 +128,9 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1386,6 +1392,68 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>対象年月初日</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>次回申請ID通番</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>シート保護パスワードは vba/modCommon.bas の SHEET_PROTECT_PASSWORD 定数で管理(運用上の誤操作防止用。真の権限管理は職員マスタのハッシュ照合で行う)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>有給の勤務コード</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1848,6 +1916,184 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>有給休暇申請</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>申請者氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>開始日</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>終了日</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>理由(任意)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>開始日〜終了日の全日程が1件の申請としてまとめて登録されます。(最大31日分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>入力後、下の「有給を申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>超過勤務(残業)申請</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>申請者氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>対象日</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>開始時刻</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>終了時刻</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>理由(任意)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>承認されると、シフト表の対象日のセルに残業時間が追記されます。(例: 日勤(残1時間30分))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>入力後、下の「残業を申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3938,7 +4184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3984,54 +4230,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>対象年月初日</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="n">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>次回申請ID通番</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>メモ</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>シート保護パスワードは vba/modCommon.bas の SHEET_PROTECT_PASSWORD 定数で管理(運用上の誤操作防止用。真の権限管理は職員マスタのハッシュ照合で行う)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/勤務変更管理システム.xlsx
+++ b/output/勤務変更管理システム.xlsx
@@ -4,22 +4,25 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="シフト表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="申請" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="承認" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ロールバック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="交換申請" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="有給申請" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="超過勤務申請" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="履歴" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="職員マスタ" sheetId="9" state="veryHidden" r:id="rId9"/>
-    <sheet name="設定" sheetId="10" state="veryHidden" r:id="rId10"/>
+    <sheet name="シフト表_入所" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="シフト表_上司" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="シフト表_通所" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="シフト表_事務局" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="申請" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="承認" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ロールバック" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="交換申請" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="有給申請" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="超過勤務申請" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="履歴" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="職員マスタ" sheetId="12" state="veryHidden" r:id="rId12"/>
+    <sheet name="設定" sheetId="13" state="veryHidden" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'履歴'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'履歴'!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -537,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>シフト表</t>
+          <t>シフト表(入所)</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -778,560 +781,11 @@
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>サンプル職員1</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>夜A</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>夜B</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>日勤</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>夜A</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>夜B</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="inlineStr"/>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr"/>
-      <c r="Z5" s="5" t="inlineStr"/>
-      <c r="AA5" s="5" t="inlineStr"/>
-      <c r="AB5" s="5" t="inlineStr"/>
-      <c r="AC5" s="5" t="inlineStr"/>
-      <c r="AD5" s="5" t="inlineStr"/>
-      <c r="AE5" s="5" t="inlineStr"/>
-      <c r="AF5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>サンプル職員2</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>夜A</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>夜B</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>日勤</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>夜A</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>夜B</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr"/>
-      <c r="W6" s="5" t="inlineStr"/>
-      <c r="X6" s="5" t="inlineStr"/>
-      <c r="Y6" s="5" t="inlineStr"/>
-      <c r="Z6" s="5" t="inlineStr"/>
-      <c r="AA6" s="5" t="inlineStr"/>
-      <c r="AB6" s="5" t="inlineStr"/>
-      <c r="AC6" s="5" t="inlineStr"/>
-      <c r="AD6" s="5" t="inlineStr"/>
-      <c r="AE6" s="5" t="inlineStr"/>
-      <c r="AF6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>サンプル職員3</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>夜B</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>日勤</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>夜A</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>夜B</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>日勤</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="inlineStr"/>
-      <c r="W7" s="5" t="inlineStr"/>
-      <c r="X7" s="5" t="inlineStr"/>
-      <c r="Y7" s="5" t="inlineStr"/>
-      <c r="Z7" s="5" t="inlineStr"/>
-      <c r="AA7" s="5" t="inlineStr"/>
-      <c r="AB7" s="5" t="inlineStr"/>
-      <c r="AC7" s="5" t="inlineStr"/>
-      <c r="AD7" s="5" t="inlineStr"/>
-      <c r="AE7" s="5" t="inlineStr"/>
-      <c r="AF7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>サンプル職員4</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>日勤</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>夜A</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>夜B</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>日勤</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="inlineStr"/>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr"/>
-      <c r="Y8" s="5" t="inlineStr"/>
-      <c r="Z8" s="5" t="inlineStr"/>
-      <c r="AA8" s="5" t="inlineStr"/>
-      <c r="AB8" s="5" t="inlineStr"/>
-      <c r="AC8" s="5" t="inlineStr"/>
-      <c r="AD8" s="5" t="inlineStr"/>
-      <c r="AE8" s="5" t="inlineStr"/>
-      <c r="AF8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>サンプル職員5</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>日勤</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>夜A</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>夜B</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>夜C</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>遅</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>研</t>
-        </is>
-      </c>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr">
-        <is>
-          <t>日勤</t>
-        </is>
-      </c>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>夜A</t>
-        </is>
-      </c>
-      <c r="V9" s="5" t="inlineStr"/>
-      <c r="W9" s="5" t="inlineStr"/>
-      <c r="X9" s="5" t="inlineStr"/>
-      <c r="Y9" s="5" t="inlineStr"/>
-      <c r="Z9" s="5" t="inlineStr"/>
-      <c r="AA9" s="5" t="inlineStr"/>
-      <c r="AB9" s="5" t="inlineStr"/>
-      <c r="AC9" s="5" t="inlineStr"/>
-      <c r="AD9" s="5" t="inlineStr"/>
-      <c r="AE9" s="5" t="inlineStr"/>
-      <c r="AF9" s="5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
@@ -1398,614 +852,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>対象年月初日</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="n">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>次回申請ID通番</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>メモ</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>シート保護パスワードは vba/modCommon.bas の SHEET_PROTECT_PASSWORD 定数で管理(運用上の誤操作防止用。真の権限管理は職員マスタのハッシュ照合で行う)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>有給の勤務コード</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>勤務変更申請</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>申請者氏名</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>パスワード</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>対象日</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>現在の勤務(自動表示)</t>
-        </is>
-      </c>
-      <c r="B6" s="10">
-        <f>IFERROR(INDEX(シフト表!$B$5:$AF$200,MATCH($B$3,シフト表!$A$5:$A$200,0),MATCH(DAY($B$5),シフト表!$B$3:$AF$3,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>変更後の勤務</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>変更理由(任意)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>入力後、下の「申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A10:F10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>勤務変更 承認</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>対象申請ID</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>承認待ち一覧からIDを選択</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>承認者氏名</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>パスワード</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>判定(承認/却下)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>▼ 承認待ち一覧(自動更新)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>申請ID</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>申請者</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>対象者</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>対象日</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>変更前</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>変更後</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>変更理由</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>申請日時</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"承認,却下"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>承認済み変更の取り消し(ロールバック)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>対象申請ID</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>承認済み一覧からIDを選択</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>承認者氏名</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>取り消しにも承認権限者のパスワードが必要です</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>パスワード</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>▼ 承認済み一覧(自動更新)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>申請ID</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>申請者</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>対象者</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>対象日</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>変更前</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>変更後(現在値)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>承認者</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>承認日時</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>勤務交換申請(2名間の振替)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>申請者氏名</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>パスワード</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>【対象者A】氏名</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>対象日A</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>現在の勤務A(自動表示)</t>
-        </is>
-      </c>
-      <c r="B8" s="10">
-        <f>IFERROR(INDEX(シフト表!$B$5:$AF$200,MATCH($B$7,シフト表!$A$5:$A$200,0),MATCH(DAY($B$8),シフト表!$B$3:$AF$3,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>変更後の勤務A</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>【対象者B】氏名</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>対象日B</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>現在の勤務B(自動表示)</t>
-        </is>
-      </c>
-      <c r="B13" s="10">
-        <f>IFERROR(INDEX(シフト表!$B$5:$AF$200,MATCH($B$12,シフト表!$A$5:$A$200,0),MATCH(DAY($B$13),シフト表!$B$3:$AF$3,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>変更後の勤務B</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>交換理由(任意)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>入力後、下の「交換を申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A18:F18"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>有給休暇申請</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>申請者氏名</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>パスワード</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>開始日</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>終了日</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>理由(任意)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>開始日〜終了日の全日程が1件の申請としてまとめて登録されます。(最大31日分)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>入力後、下の「有給を申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A9:F9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2093,7 +939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4184,7 +3030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4230,4 +3076,1668 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>対象年月初日</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>次回申請ID通番</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>シート保護パスワードは vba/modCommon.bas の SHEET_PROTECT_PASSWORD 定数で管理(運用上の誤操作防止用。真の権限管理は職員マスタのハッシュ照合で行う)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>有給の勤務コード</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="27" max="27"/>
+    <col width="5" customWidth="1" min="28" max="28"/>
+    <col width="5" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>シフト表(上司)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>対象年月(設定シートB1で変更)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>職員氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>曜日</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>IF(B$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),B$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>IF(C$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),C$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>IF(D$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),D$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>IF(E$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),E$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>IF(F$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),F$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>IF(G$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),G$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="5">
+        <f>IF(H$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),H$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="5">
+        <f>IF(I$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),I$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="5">
+        <f>IF(J$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),J$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="5">
+        <f>IF(K$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),K$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="5">
+        <f>IF(L$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),L$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="M4" s="5">
+        <f>IF(M$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),M$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="5">
+        <f>IF(N$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),N$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="O4" s="5">
+        <f>IF(O$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),O$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="P4" s="5">
+        <f>IF(P$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),P$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="5">
+        <f>IF(Q$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Q$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="R4" s="5">
+        <f>IF(R$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),R$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="S4" s="5">
+        <f>IF(S$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),S$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="T4" s="5">
+        <f>IF(T$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),T$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="U4" s="5">
+        <f>IF(U$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),U$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="V4" s="5">
+        <f>IF(V$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),V$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="W4" s="5">
+        <f>IF(W$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),W$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="X4" s="5">
+        <f>IF(X$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),X$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Y4" s="5">
+        <f>IF(Y$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Y$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Z4" s="5">
+        <f>IF(Z$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Z$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AA4" s="5">
+        <f>IF(AA$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AA$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="5">
+        <f>IF(AB$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AB$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AC4" s="5">
+        <f>IF(AC$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AC$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>IF(AD$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AD$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AE4" s="5">
+        <f>IF(AE$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AE$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AF4" s="5">
+        <f>IF(AF$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AF$3),"aaa"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="27" max="27"/>
+    <col width="5" customWidth="1" min="28" max="28"/>
+    <col width="5" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>シフト表(通所)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>対象年月(設定シートB1で変更)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>職員氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>曜日</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>IF(B$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),B$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>IF(C$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),C$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>IF(D$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),D$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>IF(E$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),E$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>IF(F$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),F$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>IF(G$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),G$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="5">
+        <f>IF(H$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),H$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="5">
+        <f>IF(I$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),I$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="5">
+        <f>IF(J$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),J$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="5">
+        <f>IF(K$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),K$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="5">
+        <f>IF(L$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),L$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="M4" s="5">
+        <f>IF(M$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),M$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="5">
+        <f>IF(N$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),N$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="O4" s="5">
+        <f>IF(O$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),O$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="P4" s="5">
+        <f>IF(P$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),P$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="5">
+        <f>IF(Q$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Q$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="R4" s="5">
+        <f>IF(R$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),R$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="S4" s="5">
+        <f>IF(S$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),S$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="T4" s="5">
+        <f>IF(T$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),T$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="U4" s="5">
+        <f>IF(U$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),U$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="V4" s="5">
+        <f>IF(V$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),V$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="W4" s="5">
+        <f>IF(W$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),W$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="X4" s="5">
+        <f>IF(X$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),X$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Y4" s="5">
+        <f>IF(Y$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Y$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Z4" s="5">
+        <f>IF(Z$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Z$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AA4" s="5">
+        <f>IF(AA$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AA$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="5">
+        <f>IF(AB$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AB$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AC4" s="5">
+        <f>IF(AC$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AC$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>IF(AD$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AD$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AE4" s="5">
+        <f>IF(AE$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AE$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AF4" s="5">
+        <f>IF(AF$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AF$3),"aaa"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="27" max="27"/>
+    <col width="5" customWidth="1" min="28" max="28"/>
+    <col width="5" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>シフト表(事務局)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>対象年月(設定シートB1で変更)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>職員氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>曜日</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>IF(B$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),B$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>IF(C$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),C$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>IF(D$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),D$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>IF(E$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),E$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>IF(F$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),F$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>IF(G$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),G$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="5">
+        <f>IF(H$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),H$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="5">
+        <f>IF(I$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),I$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="5">
+        <f>IF(J$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),J$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="5">
+        <f>IF(K$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),K$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="5">
+        <f>IF(L$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),L$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="M4" s="5">
+        <f>IF(M$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),M$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="5">
+        <f>IF(N$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),N$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="O4" s="5">
+        <f>IF(O$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),O$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="P4" s="5">
+        <f>IF(P$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),P$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="5">
+        <f>IF(Q$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Q$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="R4" s="5">
+        <f>IF(R$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),R$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="S4" s="5">
+        <f>IF(S$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),S$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="T4" s="5">
+        <f>IF(T$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),T$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="U4" s="5">
+        <f>IF(U$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),U$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="V4" s="5">
+        <f>IF(V$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),V$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="W4" s="5">
+        <f>IF(W$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),W$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="X4" s="5">
+        <f>IF(X$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),X$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Y4" s="5">
+        <f>IF(Y$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Y$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="Z4" s="5">
+        <f>IF(Z$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),Z$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AA4" s="5">
+        <f>IF(AA$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AA$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="5">
+        <f>IF(AB$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AB$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AC4" s="5">
+        <f>IF(AC$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AC$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>IF(AD$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AD$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AE4" s="5">
+        <f>IF(AE$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AE$3),"aaa"),"")</f>
+        <v/>
+      </c>
+      <c r="AF4" s="5">
+        <f>IF(AF$3&lt;=DAY(EOMONTH(設定!$B$1,0)),TEXT(DATE(YEAR(設定!$B$1),MONTH(設定!$B$1),AF$3),"aaa"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>勤務変更申請</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>申請者氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>対象日</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>現在の勤務(自動表示)</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <f>IFERROR(GetCurrentShift($B$3,$B$5),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>変更後の勤務</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>変更理由(任意)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>入力後、下の「申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>勤務変更 承認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>対象申請ID</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>承認待ち一覧からIDを選択</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>承認者氏名</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>判定(承認/却下)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>▼ 承認待ち一覧(自動更新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>申請ID</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>申請者</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>対象者</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>対象日</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>変更前</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>変更後</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>変更理由</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>申請日時</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"承認,却下"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>承認済み変更の取り消し(ロールバック)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>対象申請ID</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>承認済み一覧からIDを選択</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>承認者氏名</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>取り消しにも承認権限者のパスワードが必要です</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>▼ 承認済み一覧(自動更新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>申請ID</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>申請者</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>対象者</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>対象日</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>変更前</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>変更後(現在値)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>承認者</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>承認日時</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>勤務交換申請(2名間の振替)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>申請者氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>【対象者A】氏名</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>対象日A</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>現在の勤務A(自動表示)</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <f>IFERROR(GetCurrentShift($B$7,$B$8),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>変更後の勤務A</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>【対象者B】氏名</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>対象日B</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>現在の勤務B(自動表示)</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <f>IFERROR(GetCurrentShift($B$12,$B$13),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>変更後の勤務B</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>交換理由(任意)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>入力後、下の「交換を申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>有給休暇申請</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>申請者氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>開始日</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>終了日</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>理由(任意)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>開始日〜終了日の全日程が1件の申請としてまとめて登録されます。(最大31日分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>入力後、下の「有給を申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/勤務変更管理システム.xlsx
+++ b/output/勤務変更管理システム.xlsx
@@ -17,12 +17,13 @@
     <sheet name="交換申請" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="有給申請" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="超過勤務申請" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="履歴" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="職員マスタ" sheetId="12" state="veryHidden" r:id="rId12"/>
-    <sheet name="設定" sheetId="13" state="veryHidden" r:id="rId13"/>
+    <sheet name="管理" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="履歴" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="職員マスタ" sheetId="13" state="veryHidden" r:id="rId13"/>
+    <sheet name="設定" sheetId="14" state="veryHidden" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'履歴'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'履歴'!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -940,6 +941,56 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>月初めの切り替え</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>職員マスタ(氏名・パスワード)はそのまま残し、各部署のシフト表の中身だけを</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>消去して、新しい対象年月に切り替えます。履歴は変更されません。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3030,7 +3081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3078,7 +3129,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/勤務変更管理システム.xlsx
+++ b/output/勤務変更管理システム.xlsx
@@ -19,11 +19,17 @@
     <sheet name="超過勤務申請" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="管理" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="履歴" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="職員マスタ" sheetId="13" state="veryHidden" r:id="rId13"/>
-    <sheet name="設定" sheetId="14" state="veryHidden" r:id="rId14"/>
+    <sheet name="勤務変更履歴" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="有給履歴" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="残業履歴" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="職員マスタ" sheetId="16" state="veryHidden" r:id="rId16"/>
+    <sheet name="設定" sheetId="17" state="veryHidden" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'履歴'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'履歴'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'勤務変更履歴'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'有給履歴'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'残業履歴'!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -991,6 +997,2103 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2000"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>申請ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>申請日時</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>申請者</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>対象者</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>対象日</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>変更前</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>変更後</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>変更理由</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>承認者</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>承認/処理日時</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>元申請ID(ロールバック用)</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
+    <row r="1122"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164"/>
+    <row r="1165"/>
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
+    <row r="1178"/>
+    <row r="1179"/>
+    <row r="1180"/>
+    <row r="1181"/>
+    <row r="1182"/>
+    <row r="1183"/>
+    <row r="1184"/>
+    <row r="1185"/>
+    <row r="1186"/>
+    <row r="1187"/>
+    <row r="1188"/>
+    <row r="1189"/>
+    <row r="1190"/>
+    <row r="1191"/>
+    <row r="1192"/>
+    <row r="1193"/>
+    <row r="1194"/>
+    <row r="1195"/>
+    <row r="1196"/>
+    <row r="1197"/>
+    <row r="1198"/>
+    <row r="1199"/>
+    <row r="1200"/>
+    <row r="1201"/>
+    <row r="1202"/>
+    <row r="1203"/>
+    <row r="1204"/>
+    <row r="1205"/>
+    <row r="1206"/>
+    <row r="1207"/>
+    <row r="1208"/>
+    <row r="1209"/>
+    <row r="1210"/>
+    <row r="1211"/>
+    <row r="1212"/>
+    <row r="1213"/>
+    <row r="1214"/>
+    <row r="1215"/>
+    <row r="1216"/>
+    <row r="1217"/>
+    <row r="1218"/>
+    <row r="1219"/>
+    <row r="1220"/>
+    <row r="1221"/>
+    <row r="1222"/>
+    <row r="1223"/>
+    <row r="1224"/>
+    <row r="1225"/>
+    <row r="1226"/>
+    <row r="1227"/>
+    <row r="1228"/>
+    <row r="1229"/>
+    <row r="1230"/>
+    <row r="1231"/>
+    <row r="1232"/>
+    <row r="1233"/>
+    <row r="1234"/>
+    <row r="1235"/>
+    <row r="1236"/>
+    <row r="1237"/>
+    <row r="1238"/>
+    <row r="1239"/>
+    <row r="1240"/>
+    <row r="1241"/>
+    <row r="1242"/>
+    <row r="1243"/>
+    <row r="1244"/>
+    <row r="1245"/>
+    <row r="1246"/>
+    <row r="1247"/>
+    <row r="1248"/>
+    <row r="1249"/>
+    <row r="1250"/>
+    <row r="1251"/>
+    <row r="1252"/>
+    <row r="1253"/>
+    <row r="1254"/>
+    <row r="1255"/>
+    <row r="1256"/>
+    <row r="1257"/>
+    <row r="1258"/>
+    <row r="1259"/>
+    <row r="1260"/>
+    <row r="1261"/>
+    <row r="1262"/>
+    <row r="1263"/>
+    <row r="1264"/>
+    <row r="1265"/>
+    <row r="1266"/>
+    <row r="1267"/>
+    <row r="1268"/>
+    <row r="1269"/>
+    <row r="1270"/>
+    <row r="1271"/>
+    <row r="1272"/>
+    <row r="1273"/>
+    <row r="1274"/>
+    <row r="1275"/>
+    <row r="1276"/>
+    <row r="1277"/>
+    <row r="1278"/>
+    <row r="1279"/>
+    <row r="1280"/>
+    <row r="1281"/>
+    <row r="1282"/>
+    <row r="1283"/>
+    <row r="1284"/>
+    <row r="1285"/>
+    <row r="1286"/>
+    <row r="1287"/>
+    <row r="1288"/>
+    <row r="1289"/>
+    <row r="1290"/>
+    <row r="1291"/>
+    <row r="1292"/>
+    <row r="1293"/>
+    <row r="1294"/>
+    <row r="1295"/>
+    <row r="1296"/>
+    <row r="1297"/>
+    <row r="1298"/>
+    <row r="1299"/>
+    <row r="1300"/>
+    <row r="1301"/>
+    <row r="1302"/>
+    <row r="1303"/>
+    <row r="1304"/>
+    <row r="1305"/>
+    <row r="1306"/>
+    <row r="1307"/>
+    <row r="1308"/>
+    <row r="1309"/>
+    <row r="1310"/>
+    <row r="1311"/>
+    <row r="1312"/>
+    <row r="1313"/>
+    <row r="1314"/>
+    <row r="1315"/>
+    <row r="1316"/>
+    <row r="1317"/>
+    <row r="1318"/>
+    <row r="1319"/>
+    <row r="1320"/>
+    <row r="1321"/>
+    <row r="1322"/>
+    <row r="1323"/>
+    <row r="1324"/>
+    <row r="1325"/>
+    <row r="1326"/>
+    <row r="1327"/>
+    <row r="1328"/>
+    <row r="1329"/>
+    <row r="1330"/>
+    <row r="1331"/>
+    <row r="1332"/>
+    <row r="1333"/>
+    <row r="1334"/>
+    <row r="1335"/>
+    <row r="1336"/>
+    <row r="1337"/>
+    <row r="1338"/>
+    <row r="1339"/>
+    <row r="1340"/>
+    <row r="1341"/>
+    <row r="1342"/>
+    <row r="1343"/>
+    <row r="1344"/>
+    <row r="1345"/>
+    <row r="1346"/>
+    <row r="1347"/>
+    <row r="1348"/>
+    <row r="1349"/>
+    <row r="1350"/>
+    <row r="1351"/>
+    <row r="1352"/>
+    <row r="1353"/>
+    <row r="1354"/>
+    <row r="1355"/>
+    <row r="1356"/>
+    <row r="1357"/>
+    <row r="1358"/>
+    <row r="1359"/>
+    <row r="1360"/>
+    <row r="1361"/>
+    <row r="1362"/>
+    <row r="1363"/>
+    <row r="1364"/>
+    <row r="1365"/>
+    <row r="1366"/>
+    <row r="1367"/>
+    <row r="1368"/>
+    <row r="1369"/>
+    <row r="1370"/>
+    <row r="1371"/>
+    <row r="1372"/>
+    <row r="1373"/>
+    <row r="1374"/>
+    <row r="1375"/>
+    <row r="1376"/>
+    <row r="1377"/>
+    <row r="1378"/>
+    <row r="1379"/>
+    <row r="1380"/>
+    <row r="1381"/>
+    <row r="1382"/>
+    <row r="1383"/>
+    <row r="1384"/>
+    <row r="1385"/>
+    <row r="1386"/>
+    <row r="1387"/>
+    <row r="1388"/>
+    <row r="1389"/>
+    <row r="1390"/>
+    <row r="1391"/>
+    <row r="1392"/>
+    <row r="1393"/>
+    <row r="1394"/>
+    <row r="1395"/>
+    <row r="1396"/>
+    <row r="1397"/>
+    <row r="1398"/>
+    <row r="1399"/>
+    <row r="1400"/>
+    <row r="1401"/>
+    <row r="1402"/>
+    <row r="1403"/>
+    <row r="1404"/>
+    <row r="1405"/>
+    <row r="1406"/>
+    <row r="1407"/>
+    <row r="1408"/>
+    <row r="1409"/>
+    <row r="1410"/>
+    <row r="1411"/>
+    <row r="1412"/>
+    <row r="1413"/>
+    <row r="1414"/>
+    <row r="1415"/>
+    <row r="1416"/>
+    <row r="1417"/>
+    <row r="1418"/>
+    <row r="1419"/>
+    <row r="1420"/>
+    <row r="1421"/>
+    <row r="1422"/>
+    <row r="1423"/>
+    <row r="1424"/>
+    <row r="1425"/>
+    <row r="1426"/>
+    <row r="1427"/>
+    <row r="1428"/>
+    <row r="1429"/>
+    <row r="1430"/>
+    <row r="1431"/>
+    <row r="1432"/>
+    <row r="1433"/>
+    <row r="1434"/>
+    <row r="1435"/>
+    <row r="1436"/>
+    <row r="1437"/>
+    <row r="1438"/>
+    <row r="1439"/>
+    <row r="1440"/>
+    <row r="1441"/>
+    <row r="1442"/>
+    <row r="1443"/>
+    <row r="1444"/>
+    <row r="1445"/>
+    <row r="1446"/>
+    <row r="1447"/>
+    <row r="1448"/>
+    <row r="1449"/>
+    <row r="1450"/>
+    <row r="1451"/>
+    <row r="1452"/>
+    <row r="1453"/>
+    <row r="1454"/>
+    <row r="1455"/>
+    <row r="1456"/>
+    <row r="1457"/>
+    <row r="1458"/>
+    <row r="1459"/>
+    <row r="1460"/>
+    <row r="1461"/>
+    <row r="1462"/>
+    <row r="1463"/>
+    <row r="1464"/>
+    <row r="1465"/>
+    <row r="1466"/>
+    <row r="1467"/>
+    <row r="1468"/>
+    <row r="1469"/>
+    <row r="1470"/>
+    <row r="1471"/>
+    <row r="1472"/>
+    <row r="1473"/>
+    <row r="1474"/>
+    <row r="1475"/>
+    <row r="1476"/>
+    <row r="1477"/>
+    <row r="1478"/>
+    <row r="1479"/>
+    <row r="1480"/>
+    <row r="1481"/>
+    <row r="1482"/>
+    <row r="1483"/>
+    <row r="1484"/>
+    <row r="1485"/>
+    <row r="1486"/>
+    <row r="1487"/>
+    <row r="1488"/>
+    <row r="1489"/>
+    <row r="1490"/>
+    <row r="1491"/>
+    <row r="1492"/>
+    <row r="1493"/>
+    <row r="1494"/>
+    <row r="1495"/>
+    <row r="1496"/>
+    <row r="1497"/>
+    <row r="1498"/>
+    <row r="1499"/>
+    <row r="1500"/>
+    <row r="1501"/>
+    <row r="1502"/>
+    <row r="1503"/>
+    <row r="1504"/>
+    <row r="1505"/>
+    <row r="1506"/>
+    <row r="1507"/>
+    <row r="1508"/>
+    <row r="1509"/>
+    <row r="1510"/>
+    <row r="1511"/>
+    <row r="1512"/>
+    <row r="1513"/>
+    <row r="1514"/>
+    <row r="1515"/>
+    <row r="1516"/>
+    <row r="1517"/>
+    <row r="1518"/>
+    <row r="1519"/>
+    <row r="1520"/>
+    <row r="1521"/>
+    <row r="1522"/>
+    <row r="1523"/>
+    <row r="1524"/>
+    <row r="1525"/>
+    <row r="1526"/>
+    <row r="1527"/>
+    <row r="1528"/>
+    <row r="1529"/>
+    <row r="1530"/>
+    <row r="1531"/>
+    <row r="1532"/>
+    <row r="1533"/>
+    <row r="1534"/>
+    <row r="1535"/>
+    <row r="1536"/>
+    <row r="1537"/>
+    <row r="1538"/>
+    <row r="1539"/>
+    <row r="1540"/>
+    <row r="1541"/>
+    <row r="1542"/>
+    <row r="1543"/>
+    <row r="1544"/>
+    <row r="1545"/>
+    <row r="1546"/>
+    <row r="1547"/>
+    <row r="1548"/>
+    <row r="1549"/>
+    <row r="1550"/>
+    <row r="1551"/>
+    <row r="1552"/>
+    <row r="1553"/>
+    <row r="1554"/>
+    <row r="1555"/>
+    <row r="1556"/>
+    <row r="1557"/>
+    <row r="1558"/>
+    <row r="1559"/>
+    <row r="1560"/>
+    <row r="1561"/>
+    <row r="1562"/>
+    <row r="1563"/>
+    <row r="1564"/>
+    <row r="1565"/>
+    <row r="1566"/>
+    <row r="1567"/>
+    <row r="1568"/>
+    <row r="1569"/>
+    <row r="1570"/>
+    <row r="1571"/>
+    <row r="1572"/>
+    <row r="1573"/>
+    <row r="1574"/>
+    <row r="1575"/>
+    <row r="1576"/>
+    <row r="1577"/>
+    <row r="1578"/>
+    <row r="1579"/>
+    <row r="1580"/>
+    <row r="1581"/>
+    <row r="1582"/>
+    <row r="1583"/>
+    <row r="1584"/>
+    <row r="1585"/>
+    <row r="1586"/>
+    <row r="1587"/>
+    <row r="1588"/>
+    <row r="1589"/>
+    <row r="1590"/>
+    <row r="1591"/>
+    <row r="1592"/>
+    <row r="1593"/>
+    <row r="1594"/>
+    <row r="1595"/>
+    <row r="1596"/>
+    <row r="1597"/>
+    <row r="1598"/>
+    <row r="1599"/>
+    <row r="1600"/>
+    <row r="1601"/>
+    <row r="1602"/>
+    <row r="1603"/>
+    <row r="1604"/>
+    <row r="1605"/>
+    <row r="1606"/>
+    <row r="1607"/>
+    <row r="1608"/>
+    <row r="1609"/>
+    <row r="1610"/>
+    <row r="1611"/>
+    <row r="1612"/>
+    <row r="1613"/>
+    <row r="1614"/>
+    <row r="1615"/>
+    <row r="1616"/>
+    <row r="1617"/>
+    <row r="1618"/>
+    <row r="1619"/>
+    <row r="1620"/>
+    <row r="1621"/>
+    <row r="1622"/>
+    <row r="1623"/>
+    <row r="1624"/>
+    <row r="1625"/>
+    <row r="1626"/>
+    <row r="1627"/>
+    <row r="1628"/>
+    <row r="1629"/>
+    <row r="1630"/>
+    <row r="1631"/>
+    <row r="1632"/>
+    <row r="1633"/>
+    <row r="1634"/>
+    <row r="1635"/>
+    <row r="1636"/>
+    <row r="1637"/>
+    <row r="1638"/>
+    <row r="1639"/>
+    <row r="1640"/>
+    <row r="1641"/>
+    <row r="1642"/>
+    <row r="1643"/>
+    <row r="1644"/>
+    <row r="1645"/>
+    <row r="1646"/>
+    <row r="1647"/>
+    <row r="1648"/>
+    <row r="1649"/>
+    <row r="1650"/>
+    <row r="1651"/>
+    <row r="1652"/>
+    <row r="1653"/>
+    <row r="1654"/>
+    <row r="1655"/>
+    <row r="1656"/>
+    <row r="1657"/>
+    <row r="1658"/>
+    <row r="1659"/>
+    <row r="1660"/>
+    <row r="1661"/>
+    <row r="1662"/>
+    <row r="1663"/>
+    <row r="1664"/>
+    <row r="1665"/>
+    <row r="1666"/>
+    <row r="1667"/>
+    <row r="1668"/>
+    <row r="1669"/>
+    <row r="1670"/>
+    <row r="1671"/>
+    <row r="1672"/>
+    <row r="1673"/>
+    <row r="1674"/>
+    <row r="1675"/>
+    <row r="1676"/>
+    <row r="1677"/>
+    <row r="1678"/>
+    <row r="1679"/>
+    <row r="1680"/>
+    <row r="1681"/>
+    <row r="1682"/>
+    <row r="1683"/>
+    <row r="1684"/>
+    <row r="1685"/>
+    <row r="1686"/>
+    <row r="1687"/>
+    <row r="1688"/>
+    <row r="1689"/>
+    <row r="1690"/>
+    <row r="1691"/>
+    <row r="1692"/>
+    <row r="1693"/>
+    <row r="1694"/>
+    <row r="1695"/>
+    <row r="1696"/>
+    <row r="1697"/>
+    <row r="1698"/>
+    <row r="1699"/>
+    <row r="1700"/>
+    <row r="1701"/>
+    <row r="1702"/>
+    <row r="1703"/>
+    <row r="1704"/>
+    <row r="1705"/>
+    <row r="1706"/>
+    <row r="1707"/>
+    <row r="1708"/>
+    <row r="1709"/>
+    <row r="1710"/>
+    <row r="1711"/>
+    <row r="1712"/>
+    <row r="1713"/>
+    <row r="1714"/>
+    <row r="1715"/>
+    <row r="1716"/>
+    <row r="1717"/>
+    <row r="1718"/>
+    <row r="1719"/>
+    <row r="1720"/>
+    <row r="1721"/>
+    <row r="1722"/>
+    <row r="1723"/>
+    <row r="1724"/>
+    <row r="1725"/>
+    <row r="1726"/>
+    <row r="1727"/>
+    <row r="1728"/>
+    <row r="1729"/>
+    <row r="1730"/>
+    <row r="1731"/>
+    <row r="1732"/>
+    <row r="1733"/>
+    <row r="1734"/>
+    <row r="1735"/>
+    <row r="1736"/>
+    <row r="1737"/>
+    <row r="1738"/>
+    <row r="1739"/>
+    <row r="1740"/>
+    <row r="1741"/>
+    <row r="1742"/>
+    <row r="1743"/>
+    <row r="1744"/>
+    <row r="1745"/>
+    <row r="1746"/>
+    <row r="1747"/>
+    <row r="1748"/>
+    <row r="1749"/>
+    <row r="1750"/>
+    <row r="1751"/>
+    <row r="1752"/>
+    <row r="1753"/>
+    <row r="1754"/>
+    <row r="1755"/>
+    <row r="1756"/>
+    <row r="1757"/>
+    <row r="1758"/>
+    <row r="1759"/>
+    <row r="1760"/>
+    <row r="1761"/>
+    <row r="1762"/>
+    <row r="1763"/>
+    <row r="1764"/>
+    <row r="1765"/>
+    <row r="1766"/>
+    <row r="1767"/>
+    <row r="1768"/>
+    <row r="1769"/>
+    <row r="1770"/>
+    <row r="1771"/>
+    <row r="1772"/>
+    <row r="1773"/>
+    <row r="1774"/>
+    <row r="1775"/>
+    <row r="1776"/>
+    <row r="1777"/>
+    <row r="1778"/>
+    <row r="1779"/>
+    <row r="1780"/>
+    <row r="1781"/>
+    <row r="1782"/>
+    <row r="1783"/>
+    <row r="1784"/>
+    <row r="1785"/>
+    <row r="1786"/>
+    <row r="1787"/>
+    <row r="1788"/>
+    <row r="1789"/>
+    <row r="1790"/>
+    <row r="1791"/>
+    <row r="1792"/>
+    <row r="1793"/>
+    <row r="1794"/>
+    <row r="1795"/>
+    <row r="1796"/>
+    <row r="1797"/>
+    <row r="1798"/>
+    <row r="1799"/>
+    <row r="1800"/>
+    <row r="1801"/>
+    <row r="1802"/>
+    <row r="1803"/>
+    <row r="1804"/>
+    <row r="1805"/>
+    <row r="1806"/>
+    <row r="1807"/>
+    <row r="1808"/>
+    <row r="1809"/>
+    <row r="1810"/>
+    <row r="1811"/>
+    <row r="1812"/>
+    <row r="1813"/>
+    <row r="1814"/>
+    <row r="1815"/>
+    <row r="1816"/>
+    <row r="1817"/>
+    <row r="1818"/>
+    <row r="1819"/>
+    <row r="1820"/>
+    <row r="1821"/>
+    <row r="1822"/>
+    <row r="1823"/>
+    <row r="1824"/>
+    <row r="1825"/>
+    <row r="1826"/>
+    <row r="1827"/>
+    <row r="1828"/>
+    <row r="1829"/>
+    <row r="1830"/>
+    <row r="1831"/>
+    <row r="1832"/>
+    <row r="1833"/>
+    <row r="1834"/>
+    <row r="1835"/>
+    <row r="1836"/>
+    <row r="1837"/>
+    <row r="1838"/>
+    <row r="1839"/>
+    <row r="1840"/>
+    <row r="1841"/>
+    <row r="1842"/>
+    <row r="1843"/>
+    <row r="1844"/>
+    <row r="1845"/>
+    <row r="1846"/>
+    <row r="1847"/>
+    <row r="1848"/>
+    <row r="1849"/>
+    <row r="1850"/>
+    <row r="1851"/>
+    <row r="1852"/>
+    <row r="1853"/>
+    <row r="1854"/>
+    <row r="1855"/>
+    <row r="1856"/>
+    <row r="1857"/>
+    <row r="1858"/>
+    <row r="1859"/>
+    <row r="1860"/>
+    <row r="1861"/>
+    <row r="1862"/>
+    <row r="1863"/>
+    <row r="1864"/>
+    <row r="1865"/>
+    <row r="1866"/>
+    <row r="1867"/>
+    <row r="1868"/>
+    <row r="1869"/>
+    <row r="1870"/>
+    <row r="1871"/>
+    <row r="1872"/>
+    <row r="1873"/>
+    <row r="1874"/>
+    <row r="1875"/>
+    <row r="1876"/>
+    <row r="1877"/>
+    <row r="1878"/>
+    <row r="1879"/>
+    <row r="1880"/>
+    <row r="1881"/>
+    <row r="1882"/>
+    <row r="1883"/>
+    <row r="1884"/>
+    <row r="1885"/>
+    <row r="1886"/>
+    <row r="1887"/>
+    <row r="1888"/>
+    <row r="1889"/>
+    <row r="1890"/>
+    <row r="1891"/>
+    <row r="1892"/>
+    <row r="1893"/>
+    <row r="1894"/>
+    <row r="1895"/>
+    <row r="1896"/>
+    <row r="1897"/>
+    <row r="1898"/>
+    <row r="1899"/>
+    <row r="1900"/>
+    <row r="1901"/>
+    <row r="1902"/>
+    <row r="1903"/>
+    <row r="1904"/>
+    <row r="1905"/>
+    <row r="1906"/>
+    <row r="1907"/>
+    <row r="1908"/>
+    <row r="1909"/>
+    <row r="1910"/>
+    <row r="1911"/>
+    <row r="1912"/>
+    <row r="1913"/>
+    <row r="1914"/>
+    <row r="1915"/>
+    <row r="1916"/>
+    <row r="1917"/>
+    <row r="1918"/>
+    <row r="1919"/>
+    <row r="1920"/>
+    <row r="1921"/>
+    <row r="1922"/>
+    <row r="1923"/>
+    <row r="1924"/>
+    <row r="1925"/>
+    <row r="1926"/>
+    <row r="1927"/>
+    <row r="1928"/>
+    <row r="1929"/>
+    <row r="1930"/>
+    <row r="1931"/>
+    <row r="1932"/>
+    <row r="1933"/>
+    <row r="1934"/>
+    <row r="1935"/>
+    <row r="1936"/>
+    <row r="1937"/>
+    <row r="1938"/>
+    <row r="1939"/>
+    <row r="1940"/>
+    <row r="1941"/>
+    <row r="1942"/>
+    <row r="1943"/>
+    <row r="1944"/>
+    <row r="1945"/>
+    <row r="1946"/>
+    <row r="1947"/>
+    <row r="1948"/>
+    <row r="1949"/>
+    <row r="1950"/>
+    <row r="1951"/>
+    <row r="1952"/>
+    <row r="1953"/>
+    <row r="1954"/>
+    <row r="1955"/>
+    <row r="1956"/>
+    <row r="1957"/>
+    <row r="1958"/>
+    <row r="1959"/>
+    <row r="1960"/>
+    <row r="1961"/>
+    <row r="1962"/>
+    <row r="1963"/>
+    <row r="1964"/>
+    <row r="1965"/>
+    <row r="1966"/>
+    <row r="1967"/>
+    <row r="1968"/>
+    <row r="1969"/>
+    <row r="1970"/>
+    <row r="1971"/>
+    <row r="1972"/>
+    <row r="1973"/>
+    <row r="1974"/>
+    <row r="1975"/>
+    <row r="1976"/>
+    <row r="1977"/>
+    <row r="1978"/>
+    <row r="1979"/>
+    <row r="1980"/>
+    <row r="1981"/>
+    <row r="1982"/>
+    <row r="1983"/>
+    <row r="1984"/>
+    <row r="1985"/>
+    <row r="1986"/>
+    <row r="1987"/>
+    <row r="1988"/>
+    <row r="1989"/>
+    <row r="1990"/>
+    <row r="1991"/>
+    <row r="1992"/>
+    <row r="1993"/>
+    <row r="1994"/>
+    <row r="1995"/>
+    <row r="1996"/>
+    <row r="1997"/>
+    <row r="1998"/>
+    <row r="1999"/>
+    <row r="2000"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <autoFilter ref="A1:M1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3081,7 +5184,4189 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2000"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>申請ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>申請日時</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>申請者</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>対象者</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>対象日</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>変更前</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>変更後</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>変更理由</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>承認者</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>承認/処理日時</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>元申請ID(ロールバック用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
+    <row r="1122"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164"/>
+    <row r="1165"/>
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
+    <row r="1178"/>
+    <row r="1179"/>
+    <row r="1180"/>
+    <row r="1181"/>
+    <row r="1182"/>
+    <row r="1183"/>
+    <row r="1184"/>
+    <row r="1185"/>
+    <row r="1186"/>
+    <row r="1187"/>
+    <row r="1188"/>
+    <row r="1189"/>
+    <row r="1190"/>
+    <row r="1191"/>
+    <row r="1192"/>
+    <row r="1193"/>
+    <row r="1194"/>
+    <row r="1195"/>
+    <row r="1196"/>
+    <row r="1197"/>
+    <row r="1198"/>
+    <row r="1199"/>
+    <row r="1200"/>
+    <row r="1201"/>
+    <row r="1202"/>
+    <row r="1203"/>
+    <row r="1204"/>
+    <row r="1205"/>
+    <row r="1206"/>
+    <row r="1207"/>
+    <row r="1208"/>
+    <row r="1209"/>
+    <row r="1210"/>
+    <row r="1211"/>
+    <row r="1212"/>
+    <row r="1213"/>
+    <row r="1214"/>
+    <row r="1215"/>
+    <row r="1216"/>
+    <row r="1217"/>
+    <row r="1218"/>
+    <row r="1219"/>
+    <row r="1220"/>
+    <row r="1221"/>
+    <row r="1222"/>
+    <row r="1223"/>
+    <row r="1224"/>
+    <row r="1225"/>
+    <row r="1226"/>
+    <row r="1227"/>
+    <row r="1228"/>
+    <row r="1229"/>
+    <row r="1230"/>
+    <row r="1231"/>
+    <row r="1232"/>
+    <row r="1233"/>
+    <row r="1234"/>
+    <row r="1235"/>
+    <row r="1236"/>
+    <row r="1237"/>
+    <row r="1238"/>
+    <row r="1239"/>
+    <row r="1240"/>
+    <row r="1241"/>
+    <row r="1242"/>
+    <row r="1243"/>
+    <row r="1244"/>
+    <row r="1245"/>
+    <row r="1246"/>
+    <row r="1247"/>
+    <row r="1248"/>
+    <row r="1249"/>
+    <row r="1250"/>
+    <row r="1251"/>
+    <row r="1252"/>
+    <row r="1253"/>
+    <row r="1254"/>
+    <row r="1255"/>
+    <row r="1256"/>
+    <row r="1257"/>
+    <row r="1258"/>
+    <row r="1259"/>
+    <row r="1260"/>
+    <row r="1261"/>
+    <row r="1262"/>
+    <row r="1263"/>
+    <row r="1264"/>
+    <row r="1265"/>
+    <row r="1266"/>
+    <row r="1267"/>
+    <row r="1268"/>
+    <row r="1269"/>
+    <row r="1270"/>
+    <row r="1271"/>
+    <row r="1272"/>
+    <row r="1273"/>
+    <row r="1274"/>
+    <row r="1275"/>
+    <row r="1276"/>
+    <row r="1277"/>
+    <row r="1278"/>
+    <row r="1279"/>
+    <row r="1280"/>
+    <row r="1281"/>
+    <row r="1282"/>
+    <row r="1283"/>
+    <row r="1284"/>
+    <row r="1285"/>
+    <row r="1286"/>
+    <row r="1287"/>
+    <row r="1288"/>
+    <row r="1289"/>
+    <row r="1290"/>
+    <row r="1291"/>
+    <row r="1292"/>
+    <row r="1293"/>
+    <row r="1294"/>
+    <row r="1295"/>
+    <row r="1296"/>
+    <row r="1297"/>
+    <row r="1298"/>
+    <row r="1299"/>
+    <row r="1300"/>
+    <row r="1301"/>
+    <row r="1302"/>
+    <row r="1303"/>
+    <row r="1304"/>
+    <row r="1305"/>
+    <row r="1306"/>
+    <row r="1307"/>
+    <row r="1308"/>
+    <row r="1309"/>
+    <row r="1310"/>
+    <row r="1311"/>
+    <row r="1312"/>
+    <row r="1313"/>
+    <row r="1314"/>
+    <row r="1315"/>
+    <row r="1316"/>
+    <row r="1317"/>
+    <row r="1318"/>
+    <row r="1319"/>
+    <row r="1320"/>
+    <row r="1321"/>
+    <row r="1322"/>
+    <row r="1323"/>
+    <row r="1324"/>
+    <row r="1325"/>
+    <row r="1326"/>
+    <row r="1327"/>
+    <row r="1328"/>
+    <row r="1329"/>
+    <row r="1330"/>
+    <row r="1331"/>
+    <row r="1332"/>
+    <row r="1333"/>
+    <row r="1334"/>
+    <row r="1335"/>
+    <row r="1336"/>
+    <row r="1337"/>
+    <row r="1338"/>
+    <row r="1339"/>
+    <row r="1340"/>
+    <row r="1341"/>
+    <row r="1342"/>
+    <row r="1343"/>
+    <row r="1344"/>
+    <row r="1345"/>
+    <row r="1346"/>
+    <row r="1347"/>
+    <row r="1348"/>
+    <row r="1349"/>
+    <row r="1350"/>
+    <row r="1351"/>
+    <row r="1352"/>
+    <row r="1353"/>
+    <row r="1354"/>
+    <row r="1355"/>
+    <row r="1356"/>
+    <row r="1357"/>
+    <row r="1358"/>
+    <row r="1359"/>
+    <row r="1360"/>
+    <row r="1361"/>
+    <row r="1362"/>
+    <row r="1363"/>
+    <row r="1364"/>
+    <row r="1365"/>
+    <row r="1366"/>
+    <row r="1367"/>
+    <row r="1368"/>
+    <row r="1369"/>
+    <row r="1370"/>
+    <row r="1371"/>
+    <row r="1372"/>
+    <row r="1373"/>
+    <row r="1374"/>
+    <row r="1375"/>
+    <row r="1376"/>
+    <row r="1377"/>
+    <row r="1378"/>
+    <row r="1379"/>
+    <row r="1380"/>
+    <row r="1381"/>
+    <row r="1382"/>
+    <row r="1383"/>
+    <row r="1384"/>
+    <row r="1385"/>
+    <row r="1386"/>
+    <row r="1387"/>
+    <row r="1388"/>
+    <row r="1389"/>
+    <row r="1390"/>
+    <row r="1391"/>
+    <row r="1392"/>
+    <row r="1393"/>
+    <row r="1394"/>
+    <row r="1395"/>
+    <row r="1396"/>
+    <row r="1397"/>
+    <row r="1398"/>
+    <row r="1399"/>
+    <row r="1400"/>
+    <row r="1401"/>
+    <row r="1402"/>
+    <row r="1403"/>
+    <row r="1404"/>
+    <row r="1405"/>
+    <row r="1406"/>
+    <row r="1407"/>
+    <row r="1408"/>
+    <row r="1409"/>
+    <row r="1410"/>
+    <row r="1411"/>
+    <row r="1412"/>
+    <row r="1413"/>
+    <row r="1414"/>
+    <row r="1415"/>
+    <row r="1416"/>
+    <row r="1417"/>
+    <row r="1418"/>
+    <row r="1419"/>
+    <row r="1420"/>
+    <row r="1421"/>
+    <row r="1422"/>
+    <row r="1423"/>
+    <row r="1424"/>
+    <row r="1425"/>
+    <row r="1426"/>
+    <row r="1427"/>
+    <row r="1428"/>
+    <row r="1429"/>
+    <row r="1430"/>
+    <row r="1431"/>
+    <row r="1432"/>
+    <row r="1433"/>
+    <row r="1434"/>
+    <row r="1435"/>
+    <row r="1436"/>
+    <row r="1437"/>
+    <row r="1438"/>
+    <row r="1439"/>
+    <row r="1440"/>
+    <row r="1441"/>
+    <row r="1442"/>
+    <row r="1443"/>
+    <row r="1444"/>
+    <row r="1445"/>
+    <row r="1446"/>
+    <row r="1447"/>
+    <row r="1448"/>
+    <row r="1449"/>
+    <row r="1450"/>
+    <row r="1451"/>
+    <row r="1452"/>
+    <row r="1453"/>
+    <row r="1454"/>
+    <row r="1455"/>
+    <row r="1456"/>
+    <row r="1457"/>
+    <row r="1458"/>
+    <row r="1459"/>
+    <row r="1460"/>
+    <row r="1461"/>
+    <row r="1462"/>
+    <row r="1463"/>
+    <row r="1464"/>
+    <row r="1465"/>
+    <row r="1466"/>
+    <row r="1467"/>
+    <row r="1468"/>
+    <row r="1469"/>
+    <row r="1470"/>
+    <row r="1471"/>
+    <row r="1472"/>
+    <row r="1473"/>
+    <row r="1474"/>
+    <row r="1475"/>
+    <row r="1476"/>
+    <row r="1477"/>
+    <row r="1478"/>
+    <row r="1479"/>
+    <row r="1480"/>
+    <row r="1481"/>
+    <row r="1482"/>
+    <row r="1483"/>
+    <row r="1484"/>
+    <row r="1485"/>
+    <row r="1486"/>
+    <row r="1487"/>
+    <row r="1488"/>
+    <row r="1489"/>
+    <row r="1490"/>
+    <row r="1491"/>
+    <row r="1492"/>
+    <row r="1493"/>
+    <row r="1494"/>
+    <row r="1495"/>
+    <row r="1496"/>
+    <row r="1497"/>
+    <row r="1498"/>
+    <row r="1499"/>
+    <row r="1500"/>
+    <row r="1501"/>
+    <row r="1502"/>
+    <row r="1503"/>
+    <row r="1504"/>
+    <row r="1505"/>
+    <row r="1506"/>
+    <row r="1507"/>
+    <row r="1508"/>
+    <row r="1509"/>
+    <row r="1510"/>
+    <row r="1511"/>
+    <row r="1512"/>
+    <row r="1513"/>
+    <row r="1514"/>
+    <row r="1515"/>
+    <row r="1516"/>
+    <row r="1517"/>
+    <row r="1518"/>
+    <row r="1519"/>
+    <row r="1520"/>
+    <row r="1521"/>
+    <row r="1522"/>
+    <row r="1523"/>
+    <row r="1524"/>
+    <row r="1525"/>
+    <row r="1526"/>
+    <row r="1527"/>
+    <row r="1528"/>
+    <row r="1529"/>
+    <row r="1530"/>
+    <row r="1531"/>
+    <row r="1532"/>
+    <row r="1533"/>
+    <row r="1534"/>
+    <row r="1535"/>
+    <row r="1536"/>
+    <row r="1537"/>
+    <row r="1538"/>
+    <row r="1539"/>
+    <row r="1540"/>
+    <row r="1541"/>
+    <row r="1542"/>
+    <row r="1543"/>
+    <row r="1544"/>
+    <row r="1545"/>
+    <row r="1546"/>
+    <row r="1547"/>
+    <row r="1548"/>
+    <row r="1549"/>
+    <row r="1550"/>
+    <row r="1551"/>
+    <row r="1552"/>
+    <row r="1553"/>
+    <row r="1554"/>
+    <row r="1555"/>
+    <row r="1556"/>
+    <row r="1557"/>
+    <row r="1558"/>
+    <row r="1559"/>
+    <row r="1560"/>
+    <row r="1561"/>
+    <row r="1562"/>
+    <row r="1563"/>
+    <row r="1564"/>
+    <row r="1565"/>
+    <row r="1566"/>
+    <row r="1567"/>
+    <row r="1568"/>
+    <row r="1569"/>
+    <row r="1570"/>
+    <row r="1571"/>
+    <row r="1572"/>
+    <row r="1573"/>
+    <row r="1574"/>
+    <row r="1575"/>
+    <row r="1576"/>
+    <row r="1577"/>
+    <row r="1578"/>
+    <row r="1579"/>
+    <row r="1580"/>
+    <row r="1581"/>
+    <row r="1582"/>
+    <row r="1583"/>
+    <row r="1584"/>
+    <row r="1585"/>
+    <row r="1586"/>
+    <row r="1587"/>
+    <row r="1588"/>
+    <row r="1589"/>
+    <row r="1590"/>
+    <row r="1591"/>
+    <row r="1592"/>
+    <row r="1593"/>
+    <row r="1594"/>
+    <row r="1595"/>
+    <row r="1596"/>
+    <row r="1597"/>
+    <row r="1598"/>
+    <row r="1599"/>
+    <row r="1600"/>
+    <row r="1601"/>
+    <row r="1602"/>
+    <row r="1603"/>
+    <row r="1604"/>
+    <row r="1605"/>
+    <row r="1606"/>
+    <row r="1607"/>
+    <row r="1608"/>
+    <row r="1609"/>
+    <row r="1610"/>
+    <row r="1611"/>
+    <row r="1612"/>
+    <row r="1613"/>
+    <row r="1614"/>
+    <row r="1615"/>
+    <row r="1616"/>
+    <row r="1617"/>
+    <row r="1618"/>
+    <row r="1619"/>
+    <row r="1620"/>
+    <row r="1621"/>
+    <row r="1622"/>
+    <row r="1623"/>
+    <row r="1624"/>
+    <row r="1625"/>
+    <row r="1626"/>
+    <row r="1627"/>
+    <row r="1628"/>
+    <row r="1629"/>
+    <row r="1630"/>
+    <row r="1631"/>
+    <row r="1632"/>
+    <row r="1633"/>
+    <row r="1634"/>
+    <row r="1635"/>
+    <row r="1636"/>
+    <row r="1637"/>
+    <row r="1638"/>
+    <row r="1639"/>
+    <row r="1640"/>
+    <row r="1641"/>
+    <row r="1642"/>
+    <row r="1643"/>
+    <row r="1644"/>
+    <row r="1645"/>
+    <row r="1646"/>
+    <row r="1647"/>
+    <row r="1648"/>
+    <row r="1649"/>
+    <row r="1650"/>
+    <row r="1651"/>
+    <row r="1652"/>
+    <row r="1653"/>
+    <row r="1654"/>
+    <row r="1655"/>
+    <row r="1656"/>
+    <row r="1657"/>
+    <row r="1658"/>
+    <row r="1659"/>
+    <row r="1660"/>
+    <row r="1661"/>
+    <row r="1662"/>
+    <row r="1663"/>
+    <row r="1664"/>
+    <row r="1665"/>
+    <row r="1666"/>
+    <row r="1667"/>
+    <row r="1668"/>
+    <row r="1669"/>
+    <row r="1670"/>
+    <row r="1671"/>
+    <row r="1672"/>
+    <row r="1673"/>
+    <row r="1674"/>
+    <row r="1675"/>
+    <row r="1676"/>
+    <row r="1677"/>
+    <row r="1678"/>
+    <row r="1679"/>
+    <row r="1680"/>
+    <row r="1681"/>
+    <row r="1682"/>
+    <row r="1683"/>
+    <row r="1684"/>
+    <row r="1685"/>
+    <row r="1686"/>
+    <row r="1687"/>
+    <row r="1688"/>
+    <row r="1689"/>
+    <row r="1690"/>
+    <row r="1691"/>
+    <row r="1692"/>
+    <row r="1693"/>
+    <row r="1694"/>
+    <row r="1695"/>
+    <row r="1696"/>
+    <row r="1697"/>
+    <row r="1698"/>
+    <row r="1699"/>
+    <row r="1700"/>
+    <row r="1701"/>
+    <row r="1702"/>
+    <row r="1703"/>
+    <row r="1704"/>
+    <row r="1705"/>
+    <row r="1706"/>
+    <row r="1707"/>
+    <row r="1708"/>
+    <row r="1709"/>
+    <row r="1710"/>
+    <row r="1711"/>
+    <row r="1712"/>
+    <row r="1713"/>
+    <row r="1714"/>
+    <row r="1715"/>
+    <row r="1716"/>
+    <row r="1717"/>
+    <row r="1718"/>
+    <row r="1719"/>
+    <row r="1720"/>
+    <row r="1721"/>
+    <row r="1722"/>
+    <row r="1723"/>
+    <row r="1724"/>
+    <row r="1725"/>
+    <row r="1726"/>
+    <row r="1727"/>
+    <row r="1728"/>
+    <row r="1729"/>
+    <row r="1730"/>
+    <row r="1731"/>
+    <row r="1732"/>
+    <row r="1733"/>
+    <row r="1734"/>
+    <row r="1735"/>
+    <row r="1736"/>
+    <row r="1737"/>
+    <row r="1738"/>
+    <row r="1739"/>
+    <row r="1740"/>
+    <row r="1741"/>
+    <row r="1742"/>
+    <row r="1743"/>
+    <row r="1744"/>
+    <row r="1745"/>
+    <row r="1746"/>
+    <row r="1747"/>
+    <row r="1748"/>
+    <row r="1749"/>
+    <row r="1750"/>
+    <row r="1751"/>
+    <row r="1752"/>
+    <row r="1753"/>
+    <row r="1754"/>
+    <row r="1755"/>
+    <row r="1756"/>
+    <row r="1757"/>
+    <row r="1758"/>
+    <row r="1759"/>
+    <row r="1760"/>
+    <row r="1761"/>
+    <row r="1762"/>
+    <row r="1763"/>
+    <row r="1764"/>
+    <row r="1765"/>
+    <row r="1766"/>
+    <row r="1767"/>
+    <row r="1768"/>
+    <row r="1769"/>
+    <row r="1770"/>
+    <row r="1771"/>
+    <row r="1772"/>
+    <row r="1773"/>
+    <row r="1774"/>
+    <row r="1775"/>
+    <row r="1776"/>
+    <row r="1777"/>
+    <row r="1778"/>
+    <row r="1779"/>
+    <row r="1780"/>
+    <row r="1781"/>
+    <row r="1782"/>
+    <row r="1783"/>
+    <row r="1784"/>
+    <row r="1785"/>
+    <row r="1786"/>
+    <row r="1787"/>
+    <row r="1788"/>
+    <row r="1789"/>
+    <row r="1790"/>
+    <row r="1791"/>
+    <row r="1792"/>
+    <row r="1793"/>
+    <row r="1794"/>
+    <row r="1795"/>
+    <row r="1796"/>
+    <row r="1797"/>
+    <row r="1798"/>
+    <row r="1799"/>
+    <row r="1800"/>
+    <row r="1801"/>
+    <row r="1802"/>
+    <row r="1803"/>
+    <row r="1804"/>
+    <row r="1805"/>
+    <row r="1806"/>
+    <row r="1807"/>
+    <row r="1808"/>
+    <row r="1809"/>
+    <row r="1810"/>
+    <row r="1811"/>
+    <row r="1812"/>
+    <row r="1813"/>
+    <row r="1814"/>
+    <row r="1815"/>
+    <row r="1816"/>
+    <row r="1817"/>
+    <row r="1818"/>
+    <row r="1819"/>
+    <row r="1820"/>
+    <row r="1821"/>
+    <row r="1822"/>
+    <row r="1823"/>
+    <row r="1824"/>
+    <row r="1825"/>
+    <row r="1826"/>
+    <row r="1827"/>
+    <row r="1828"/>
+    <row r="1829"/>
+    <row r="1830"/>
+    <row r="1831"/>
+    <row r="1832"/>
+    <row r="1833"/>
+    <row r="1834"/>
+    <row r="1835"/>
+    <row r="1836"/>
+    <row r="1837"/>
+    <row r="1838"/>
+    <row r="1839"/>
+    <row r="1840"/>
+    <row r="1841"/>
+    <row r="1842"/>
+    <row r="1843"/>
+    <row r="1844"/>
+    <row r="1845"/>
+    <row r="1846"/>
+    <row r="1847"/>
+    <row r="1848"/>
+    <row r="1849"/>
+    <row r="1850"/>
+    <row r="1851"/>
+    <row r="1852"/>
+    <row r="1853"/>
+    <row r="1854"/>
+    <row r="1855"/>
+    <row r="1856"/>
+    <row r="1857"/>
+    <row r="1858"/>
+    <row r="1859"/>
+    <row r="1860"/>
+    <row r="1861"/>
+    <row r="1862"/>
+    <row r="1863"/>
+    <row r="1864"/>
+    <row r="1865"/>
+    <row r="1866"/>
+    <row r="1867"/>
+    <row r="1868"/>
+    <row r="1869"/>
+    <row r="1870"/>
+    <row r="1871"/>
+    <row r="1872"/>
+    <row r="1873"/>
+    <row r="1874"/>
+    <row r="1875"/>
+    <row r="1876"/>
+    <row r="1877"/>
+    <row r="1878"/>
+    <row r="1879"/>
+    <row r="1880"/>
+    <row r="1881"/>
+    <row r="1882"/>
+    <row r="1883"/>
+    <row r="1884"/>
+    <row r="1885"/>
+    <row r="1886"/>
+    <row r="1887"/>
+    <row r="1888"/>
+    <row r="1889"/>
+    <row r="1890"/>
+    <row r="1891"/>
+    <row r="1892"/>
+    <row r="1893"/>
+    <row r="1894"/>
+    <row r="1895"/>
+    <row r="1896"/>
+    <row r="1897"/>
+    <row r="1898"/>
+    <row r="1899"/>
+    <row r="1900"/>
+    <row r="1901"/>
+    <row r="1902"/>
+    <row r="1903"/>
+    <row r="1904"/>
+    <row r="1905"/>
+    <row r="1906"/>
+    <row r="1907"/>
+    <row r="1908"/>
+    <row r="1909"/>
+    <row r="1910"/>
+    <row r="1911"/>
+    <row r="1912"/>
+    <row r="1913"/>
+    <row r="1914"/>
+    <row r="1915"/>
+    <row r="1916"/>
+    <row r="1917"/>
+    <row r="1918"/>
+    <row r="1919"/>
+    <row r="1920"/>
+    <row r="1921"/>
+    <row r="1922"/>
+    <row r="1923"/>
+    <row r="1924"/>
+    <row r="1925"/>
+    <row r="1926"/>
+    <row r="1927"/>
+    <row r="1928"/>
+    <row r="1929"/>
+    <row r="1930"/>
+    <row r="1931"/>
+    <row r="1932"/>
+    <row r="1933"/>
+    <row r="1934"/>
+    <row r="1935"/>
+    <row r="1936"/>
+    <row r="1937"/>
+    <row r="1938"/>
+    <row r="1939"/>
+    <row r="1940"/>
+    <row r="1941"/>
+    <row r="1942"/>
+    <row r="1943"/>
+    <row r="1944"/>
+    <row r="1945"/>
+    <row r="1946"/>
+    <row r="1947"/>
+    <row r="1948"/>
+    <row r="1949"/>
+    <row r="1950"/>
+    <row r="1951"/>
+    <row r="1952"/>
+    <row r="1953"/>
+    <row r="1954"/>
+    <row r="1955"/>
+    <row r="1956"/>
+    <row r="1957"/>
+    <row r="1958"/>
+    <row r="1959"/>
+    <row r="1960"/>
+    <row r="1961"/>
+    <row r="1962"/>
+    <row r="1963"/>
+    <row r="1964"/>
+    <row r="1965"/>
+    <row r="1966"/>
+    <row r="1967"/>
+    <row r="1968"/>
+    <row r="1969"/>
+    <row r="1970"/>
+    <row r="1971"/>
+    <row r="1972"/>
+    <row r="1973"/>
+    <row r="1974"/>
+    <row r="1975"/>
+    <row r="1976"/>
+    <row r="1977"/>
+    <row r="1978"/>
+    <row r="1979"/>
+    <row r="1980"/>
+    <row r="1981"/>
+    <row r="1982"/>
+    <row r="1983"/>
+    <row r="1984"/>
+    <row r="1985"/>
+    <row r="1986"/>
+    <row r="1987"/>
+    <row r="1988"/>
+    <row r="1989"/>
+    <row r="1990"/>
+    <row r="1991"/>
+    <row r="1992"/>
+    <row r="1993"/>
+    <row r="1994"/>
+    <row r="1995"/>
+    <row r="1996"/>
+    <row r="1997"/>
+    <row r="1998"/>
+    <row r="1999"/>
+    <row r="2000"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <autoFilter ref="A1:L1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2000"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>申請ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>申請日時</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>申請者</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>対象者</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>対象日</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>変更前</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>変更後</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>変更理由</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>承認者</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>承認/処理日時</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>元申請ID(ロールバック用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
+    <row r="1122"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164"/>
+    <row r="1165"/>
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
+    <row r="1178"/>
+    <row r="1179"/>
+    <row r="1180"/>
+    <row r="1181"/>
+    <row r="1182"/>
+    <row r="1183"/>
+    <row r="1184"/>
+    <row r="1185"/>
+    <row r="1186"/>
+    <row r="1187"/>
+    <row r="1188"/>
+    <row r="1189"/>
+    <row r="1190"/>
+    <row r="1191"/>
+    <row r="1192"/>
+    <row r="1193"/>
+    <row r="1194"/>
+    <row r="1195"/>
+    <row r="1196"/>
+    <row r="1197"/>
+    <row r="1198"/>
+    <row r="1199"/>
+    <row r="1200"/>
+    <row r="1201"/>
+    <row r="1202"/>
+    <row r="1203"/>
+    <row r="1204"/>
+    <row r="1205"/>
+    <row r="1206"/>
+    <row r="1207"/>
+    <row r="1208"/>
+    <row r="1209"/>
+    <row r="1210"/>
+    <row r="1211"/>
+    <row r="1212"/>
+    <row r="1213"/>
+    <row r="1214"/>
+    <row r="1215"/>
+    <row r="1216"/>
+    <row r="1217"/>
+    <row r="1218"/>
+    <row r="1219"/>
+    <row r="1220"/>
+    <row r="1221"/>
+    <row r="1222"/>
+    <row r="1223"/>
+    <row r="1224"/>
+    <row r="1225"/>
+    <row r="1226"/>
+    <row r="1227"/>
+    <row r="1228"/>
+    <row r="1229"/>
+    <row r="1230"/>
+    <row r="1231"/>
+    <row r="1232"/>
+    <row r="1233"/>
+    <row r="1234"/>
+    <row r="1235"/>
+    <row r="1236"/>
+    <row r="1237"/>
+    <row r="1238"/>
+    <row r="1239"/>
+    <row r="1240"/>
+    <row r="1241"/>
+    <row r="1242"/>
+    <row r="1243"/>
+    <row r="1244"/>
+    <row r="1245"/>
+    <row r="1246"/>
+    <row r="1247"/>
+    <row r="1248"/>
+    <row r="1249"/>
+    <row r="1250"/>
+    <row r="1251"/>
+    <row r="1252"/>
+    <row r="1253"/>
+    <row r="1254"/>
+    <row r="1255"/>
+    <row r="1256"/>
+    <row r="1257"/>
+    <row r="1258"/>
+    <row r="1259"/>
+    <row r="1260"/>
+    <row r="1261"/>
+    <row r="1262"/>
+    <row r="1263"/>
+    <row r="1264"/>
+    <row r="1265"/>
+    <row r="1266"/>
+    <row r="1267"/>
+    <row r="1268"/>
+    <row r="1269"/>
+    <row r="1270"/>
+    <row r="1271"/>
+    <row r="1272"/>
+    <row r="1273"/>
+    <row r="1274"/>
+    <row r="1275"/>
+    <row r="1276"/>
+    <row r="1277"/>
+    <row r="1278"/>
+    <row r="1279"/>
+    <row r="1280"/>
+    <row r="1281"/>
+    <row r="1282"/>
+    <row r="1283"/>
+    <row r="1284"/>
+    <row r="1285"/>
+    <row r="1286"/>
+    <row r="1287"/>
+    <row r="1288"/>
+    <row r="1289"/>
+    <row r="1290"/>
+    <row r="1291"/>
+    <row r="1292"/>
+    <row r="1293"/>
+    <row r="1294"/>
+    <row r="1295"/>
+    <row r="1296"/>
+    <row r="1297"/>
+    <row r="1298"/>
+    <row r="1299"/>
+    <row r="1300"/>
+    <row r="1301"/>
+    <row r="1302"/>
+    <row r="1303"/>
+    <row r="1304"/>
+    <row r="1305"/>
+    <row r="1306"/>
+    <row r="1307"/>
+    <row r="1308"/>
+    <row r="1309"/>
+    <row r="1310"/>
+    <row r="1311"/>
+    <row r="1312"/>
+    <row r="1313"/>
+    <row r="1314"/>
+    <row r="1315"/>
+    <row r="1316"/>
+    <row r="1317"/>
+    <row r="1318"/>
+    <row r="1319"/>
+    <row r="1320"/>
+    <row r="1321"/>
+    <row r="1322"/>
+    <row r="1323"/>
+    <row r="1324"/>
+    <row r="1325"/>
+    <row r="1326"/>
+    <row r="1327"/>
+    <row r="1328"/>
+    <row r="1329"/>
+    <row r="1330"/>
+    <row r="1331"/>
+    <row r="1332"/>
+    <row r="1333"/>
+    <row r="1334"/>
+    <row r="1335"/>
+    <row r="1336"/>
+    <row r="1337"/>
+    <row r="1338"/>
+    <row r="1339"/>
+    <row r="1340"/>
+    <row r="1341"/>
+    <row r="1342"/>
+    <row r="1343"/>
+    <row r="1344"/>
+    <row r="1345"/>
+    <row r="1346"/>
+    <row r="1347"/>
+    <row r="1348"/>
+    <row r="1349"/>
+    <row r="1350"/>
+    <row r="1351"/>
+    <row r="1352"/>
+    <row r="1353"/>
+    <row r="1354"/>
+    <row r="1355"/>
+    <row r="1356"/>
+    <row r="1357"/>
+    <row r="1358"/>
+    <row r="1359"/>
+    <row r="1360"/>
+    <row r="1361"/>
+    <row r="1362"/>
+    <row r="1363"/>
+    <row r="1364"/>
+    <row r="1365"/>
+    <row r="1366"/>
+    <row r="1367"/>
+    <row r="1368"/>
+    <row r="1369"/>
+    <row r="1370"/>
+    <row r="1371"/>
+    <row r="1372"/>
+    <row r="1373"/>
+    <row r="1374"/>
+    <row r="1375"/>
+    <row r="1376"/>
+    <row r="1377"/>
+    <row r="1378"/>
+    <row r="1379"/>
+    <row r="1380"/>
+    <row r="1381"/>
+    <row r="1382"/>
+    <row r="1383"/>
+    <row r="1384"/>
+    <row r="1385"/>
+    <row r="1386"/>
+    <row r="1387"/>
+    <row r="1388"/>
+    <row r="1389"/>
+    <row r="1390"/>
+    <row r="1391"/>
+    <row r="1392"/>
+    <row r="1393"/>
+    <row r="1394"/>
+    <row r="1395"/>
+    <row r="1396"/>
+    <row r="1397"/>
+    <row r="1398"/>
+    <row r="1399"/>
+    <row r="1400"/>
+    <row r="1401"/>
+    <row r="1402"/>
+    <row r="1403"/>
+    <row r="1404"/>
+    <row r="1405"/>
+    <row r="1406"/>
+    <row r="1407"/>
+    <row r="1408"/>
+    <row r="1409"/>
+    <row r="1410"/>
+    <row r="1411"/>
+    <row r="1412"/>
+    <row r="1413"/>
+    <row r="1414"/>
+    <row r="1415"/>
+    <row r="1416"/>
+    <row r="1417"/>
+    <row r="1418"/>
+    <row r="1419"/>
+    <row r="1420"/>
+    <row r="1421"/>
+    <row r="1422"/>
+    <row r="1423"/>
+    <row r="1424"/>
+    <row r="1425"/>
+    <row r="1426"/>
+    <row r="1427"/>
+    <row r="1428"/>
+    <row r="1429"/>
+    <row r="1430"/>
+    <row r="1431"/>
+    <row r="1432"/>
+    <row r="1433"/>
+    <row r="1434"/>
+    <row r="1435"/>
+    <row r="1436"/>
+    <row r="1437"/>
+    <row r="1438"/>
+    <row r="1439"/>
+    <row r="1440"/>
+    <row r="1441"/>
+    <row r="1442"/>
+    <row r="1443"/>
+    <row r="1444"/>
+    <row r="1445"/>
+    <row r="1446"/>
+    <row r="1447"/>
+    <row r="1448"/>
+    <row r="1449"/>
+    <row r="1450"/>
+    <row r="1451"/>
+    <row r="1452"/>
+    <row r="1453"/>
+    <row r="1454"/>
+    <row r="1455"/>
+    <row r="1456"/>
+    <row r="1457"/>
+    <row r="1458"/>
+    <row r="1459"/>
+    <row r="1460"/>
+    <row r="1461"/>
+    <row r="1462"/>
+    <row r="1463"/>
+    <row r="1464"/>
+    <row r="1465"/>
+    <row r="1466"/>
+    <row r="1467"/>
+    <row r="1468"/>
+    <row r="1469"/>
+    <row r="1470"/>
+    <row r="1471"/>
+    <row r="1472"/>
+    <row r="1473"/>
+    <row r="1474"/>
+    <row r="1475"/>
+    <row r="1476"/>
+    <row r="1477"/>
+    <row r="1478"/>
+    <row r="1479"/>
+    <row r="1480"/>
+    <row r="1481"/>
+    <row r="1482"/>
+    <row r="1483"/>
+    <row r="1484"/>
+    <row r="1485"/>
+    <row r="1486"/>
+    <row r="1487"/>
+    <row r="1488"/>
+    <row r="1489"/>
+    <row r="1490"/>
+    <row r="1491"/>
+    <row r="1492"/>
+    <row r="1493"/>
+    <row r="1494"/>
+    <row r="1495"/>
+    <row r="1496"/>
+    <row r="1497"/>
+    <row r="1498"/>
+    <row r="1499"/>
+    <row r="1500"/>
+    <row r="1501"/>
+    <row r="1502"/>
+    <row r="1503"/>
+    <row r="1504"/>
+    <row r="1505"/>
+    <row r="1506"/>
+    <row r="1507"/>
+    <row r="1508"/>
+    <row r="1509"/>
+    <row r="1510"/>
+    <row r="1511"/>
+    <row r="1512"/>
+    <row r="1513"/>
+    <row r="1514"/>
+    <row r="1515"/>
+    <row r="1516"/>
+    <row r="1517"/>
+    <row r="1518"/>
+    <row r="1519"/>
+    <row r="1520"/>
+    <row r="1521"/>
+    <row r="1522"/>
+    <row r="1523"/>
+    <row r="1524"/>
+    <row r="1525"/>
+    <row r="1526"/>
+    <row r="1527"/>
+    <row r="1528"/>
+    <row r="1529"/>
+    <row r="1530"/>
+    <row r="1531"/>
+    <row r="1532"/>
+    <row r="1533"/>
+    <row r="1534"/>
+    <row r="1535"/>
+    <row r="1536"/>
+    <row r="1537"/>
+    <row r="1538"/>
+    <row r="1539"/>
+    <row r="1540"/>
+    <row r="1541"/>
+    <row r="1542"/>
+    <row r="1543"/>
+    <row r="1544"/>
+    <row r="1545"/>
+    <row r="1546"/>
+    <row r="1547"/>
+    <row r="1548"/>
+    <row r="1549"/>
+    <row r="1550"/>
+    <row r="1551"/>
+    <row r="1552"/>
+    <row r="1553"/>
+    <row r="1554"/>
+    <row r="1555"/>
+    <row r="1556"/>
+    <row r="1557"/>
+    <row r="1558"/>
+    <row r="1559"/>
+    <row r="1560"/>
+    <row r="1561"/>
+    <row r="1562"/>
+    <row r="1563"/>
+    <row r="1564"/>
+    <row r="1565"/>
+    <row r="1566"/>
+    <row r="1567"/>
+    <row r="1568"/>
+    <row r="1569"/>
+    <row r="1570"/>
+    <row r="1571"/>
+    <row r="1572"/>
+    <row r="1573"/>
+    <row r="1574"/>
+    <row r="1575"/>
+    <row r="1576"/>
+    <row r="1577"/>
+    <row r="1578"/>
+    <row r="1579"/>
+    <row r="1580"/>
+    <row r="1581"/>
+    <row r="1582"/>
+    <row r="1583"/>
+    <row r="1584"/>
+    <row r="1585"/>
+    <row r="1586"/>
+    <row r="1587"/>
+    <row r="1588"/>
+    <row r="1589"/>
+    <row r="1590"/>
+    <row r="1591"/>
+    <row r="1592"/>
+    <row r="1593"/>
+    <row r="1594"/>
+    <row r="1595"/>
+    <row r="1596"/>
+    <row r="1597"/>
+    <row r="1598"/>
+    <row r="1599"/>
+    <row r="1600"/>
+    <row r="1601"/>
+    <row r="1602"/>
+    <row r="1603"/>
+    <row r="1604"/>
+    <row r="1605"/>
+    <row r="1606"/>
+    <row r="1607"/>
+    <row r="1608"/>
+    <row r="1609"/>
+    <row r="1610"/>
+    <row r="1611"/>
+    <row r="1612"/>
+    <row r="1613"/>
+    <row r="1614"/>
+    <row r="1615"/>
+    <row r="1616"/>
+    <row r="1617"/>
+    <row r="1618"/>
+    <row r="1619"/>
+    <row r="1620"/>
+    <row r="1621"/>
+    <row r="1622"/>
+    <row r="1623"/>
+    <row r="1624"/>
+    <row r="1625"/>
+    <row r="1626"/>
+    <row r="1627"/>
+    <row r="1628"/>
+    <row r="1629"/>
+    <row r="1630"/>
+    <row r="1631"/>
+    <row r="1632"/>
+    <row r="1633"/>
+    <row r="1634"/>
+    <row r="1635"/>
+    <row r="1636"/>
+    <row r="1637"/>
+    <row r="1638"/>
+    <row r="1639"/>
+    <row r="1640"/>
+    <row r="1641"/>
+    <row r="1642"/>
+    <row r="1643"/>
+    <row r="1644"/>
+    <row r="1645"/>
+    <row r="1646"/>
+    <row r="1647"/>
+    <row r="1648"/>
+    <row r="1649"/>
+    <row r="1650"/>
+    <row r="1651"/>
+    <row r="1652"/>
+    <row r="1653"/>
+    <row r="1654"/>
+    <row r="1655"/>
+    <row r="1656"/>
+    <row r="1657"/>
+    <row r="1658"/>
+    <row r="1659"/>
+    <row r="1660"/>
+    <row r="1661"/>
+    <row r="1662"/>
+    <row r="1663"/>
+    <row r="1664"/>
+    <row r="1665"/>
+    <row r="1666"/>
+    <row r="1667"/>
+    <row r="1668"/>
+    <row r="1669"/>
+    <row r="1670"/>
+    <row r="1671"/>
+    <row r="1672"/>
+    <row r="1673"/>
+    <row r="1674"/>
+    <row r="1675"/>
+    <row r="1676"/>
+    <row r="1677"/>
+    <row r="1678"/>
+    <row r="1679"/>
+    <row r="1680"/>
+    <row r="1681"/>
+    <row r="1682"/>
+    <row r="1683"/>
+    <row r="1684"/>
+    <row r="1685"/>
+    <row r="1686"/>
+    <row r="1687"/>
+    <row r="1688"/>
+    <row r="1689"/>
+    <row r="1690"/>
+    <row r="1691"/>
+    <row r="1692"/>
+    <row r="1693"/>
+    <row r="1694"/>
+    <row r="1695"/>
+    <row r="1696"/>
+    <row r="1697"/>
+    <row r="1698"/>
+    <row r="1699"/>
+    <row r="1700"/>
+    <row r="1701"/>
+    <row r="1702"/>
+    <row r="1703"/>
+    <row r="1704"/>
+    <row r="1705"/>
+    <row r="1706"/>
+    <row r="1707"/>
+    <row r="1708"/>
+    <row r="1709"/>
+    <row r="1710"/>
+    <row r="1711"/>
+    <row r="1712"/>
+    <row r="1713"/>
+    <row r="1714"/>
+    <row r="1715"/>
+    <row r="1716"/>
+    <row r="1717"/>
+    <row r="1718"/>
+    <row r="1719"/>
+    <row r="1720"/>
+    <row r="1721"/>
+    <row r="1722"/>
+    <row r="1723"/>
+    <row r="1724"/>
+    <row r="1725"/>
+    <row r="1726"/>
+    <row r="1727"/>
+    <row r="1728"/>
+    <row r="1729"/>
+    <row r="1730"/>
+    <row r="1731"/>
+    <row r="1732"/>
+    <row r="1733"/>
+    <row r="1734"/>
+    <row r="1735"/>
+    <row r="1736"/>
+    <row r="1737"/>
+    <row r="1738"/>
+    <row r="1739"/>
+    <row r="1740"/>
+    <row r="1741"/>
+    <row r="1742"/>
+    <row r="1743"/>
+    <row r="1744"/>
+    <row r="1745"/>
+    <row r="1746"/>
+    <row r="1747"/>
+    <row r="1748"/>
+    <row r="1749"/>
+    <row r="1750"/>
+    <row r="1751"/>
+    <row r="1752"/>
+    <row r="1753"/>
+    <row r="1754"/>
+    <row r="1755"/>
+    <row r="1756"/>
+    <row r="1757"/>
+    <row r="1758"/>
+    <row r="1759"/>
+    <row r="1760"/>
+    <row r="1761"/>
+    <row r="1762"/>
+    <row r="1763"/>
+    <row r="1764"/>
+    <row r="1765"/>
+    <row r="1766"/>
+    <row r="1767"/>
+    <row r="1768"/>
+    <row r="1769"/>
+    <row r="1770"/>
+    <row r="1771"/>
+    <row r="1772"/>
+    <row r="1773"/>
+    <row r="1774"/>
+    <row r="1775"/>
+    <row r="1776"/>
+    <row r="1777"/>
+    <row r="1778"/>
+    <row r="1779"/>
+    <row r="1780"/>
+    <row r="1781"/>
+    <row r="1782"/>
+    <row r="1783"/>
+    <row r="1784"/>
+    <row r="1785"/>
+    <row r="1786"/>
+    <row r="1787"/>
+    <row r="1788"/>
+    <row r="1789"/>
+    <row r="1790"/>
+    <row r="1791"/>
+    <row r="1792"/>
+    <row r="1793"/>
+    <row r="1794"/>
+    <row r="1795"/>
+    <row r="1796"/>
+    <row r="1797"/>
+    <row r="1798"/>
+    <row r="1799"/>
+    <row r="1800"/>
+    <row r="1801"/>
+    <row r="1802"/>
+    <row r="1803"/>
+    <row r="1804"/>
+    <row r="1805"/>
+    <row r="1806"/>
+    <row r="1807"/>
+    <row r="1808"/>
+    <row r="1809"/>
+    <row r="1810"/>
+    <row r="1811"/>
+    <row r="1812"/>
+    <row r="1813"/>
+    <row r="1814"/>
+    <row r="1815"/>
+    <row r="1816"/>
+    <row r="1817"/>
+    <row r="1818"/>
+    <row r="1819"/>
+    <row r="1820"/>
+    <row r="1821"/>
+    <row r="1822"/>
+    <row r="1823"/>
+    <row r="1824"/>
+    <row r="1825"/>
+    <row r="1826"/>
+    <row r="1827"/>
+    <row r="1828"/>
+    <row r="1829"/>
+    <row r="1830"/>
+    <row r="1831"/>
+    <row r="1832"/>
+    <row r="1833"/>
+    <row r="1834"/>
+    <row r="1835"/>
+    <row r="1836"/>
+    <row r="1837"/>
+    <row r="1838"/>
+    <row r="1839"/>
+    <row r="1840"/>
+    <row r="1841"/>
+    <row r="1842"/>
+    <row r="1843"/>
+    <row r="1844"/>
+    <row r="1845"/>
+    <row r="1846"/>
+    <row r="1847"/>
+    <row r="1848"/>
+    <row r="1849"/>
+    <row r="1850"/>
+    <row r="1851"/>
+    <row r="1852"/>
+    <row r="1853"/>
+    <row r="1854"/>
+    <row r="1855"/>
+    <row r="1856"/>
+    <row r="1857"/>
+    <row r="1858"/>
+    <row r="1859"/>
+    <row r="1860"/>
+    <row r="1861"/>
+    <row r="1862"/>
+    <row r="1863"/>
+    <row r="1864"/>
+    <row r="1865"/>
+    <row r="1866"/>
+    <row r="1867"/>
+    <row r="1868"/>
+    <row r="1869"/>
+    <row r="1870"/>
+    <row r="1871"/>
+    <row r="1872"/>
+    <row r="1873"/>
+    <row r="1874"/>
+    <row r="1875"/>
+    <row r="1876"/>
+    <row r="1877"/>
+    <row r="1878"/>
+    <row r="1879"/>
+    <row r="1880"/>
+    <row r="1881"/>
+    <row r="1882"/>
+    <row r="1883"/>
+    <row r="1884"/>
+    <row r="1885"/>
+    <row r="1886"/>
+    <row r="1887"/>
+    <row r="1888"/>
+    <row r="1889"/>
+    <row r="1890"/>
+    <row r="1891"/>
+    <row r="1892"/>
+    <row r="1893"/>
+    <row r="1894"/>
+    <row r="1895"/>
+    <row r="1896"/>
+    <row r="1897"/>
+    <row r="1898"/>
+    <row r="1899"/>
+    <row r="1900"/>
+    <row r="1901"/>
+    <row r="1902"/>
+    <row r="1903"/>
+    <row r="1904"/>
+    <row r="1905"/>
+    <row r="1906"/>
+    <row r="1907"/>
+    <row r="1908"/>
+    <row r="1909"/>
+    <row r="1910"/>
+    <row r="1911"/>
+    <row r="1912"/>
+    <row r="1913"/>
+    <row r="1914"/>
+    <row r="1915"/>
+    <row r="1916"/>
+    <row r="1917"/>
+    <row r="1918"/>
+    <row r="1919"/>
+    <row r="1920"/>
+    <row r="1921"/>
+    <row r="1922"/>
+    <row r="1923"/>
+    <row r="1924"/>
+    <row r="1925"/>
+    <row r="1926"/>
+    <row r="1927"/>
+    <row r="1928"/>
+    <row r="1929"/>
+    <row r="1930"/>
+    <row r="1931"/>
+    <row r="1932"/>
+    <row r="1933"/>
+    <row r="1934"/>
+    <row r="1935"/>
+    <row r="1936"/>
+    <row r="1937"/>
+    <row r="1938"/>
+    <row r="1939"/>
+    <row r="1940"/>
+    <row r="1941"/>
+    <row r="1942"/>
+    <row r="1943"/>
+    <row r="1944"/>
+    <row r="1945"/>
+    <row r="1946"/>
+    <row r="1947"/>
+    <row r="1948"/>
+    <row r="1949"/>
+    <row r="1950"/>
+    <row r="1951"/>
+    <row r="1952"/>
+    <row r="1953"/>
+    <row r="1954"/>
+    <row r="1955"/>
+    <row r="1956"/>
+    <row r="1957"/>
+    <row r="1958"/>
+    <row r="1959"/>
+    <row r="1960"/>
+    <row r="1961"/>
+    <row r="1962"/>
+    <row r="1963"/>
+    <row r="1964"/>
+    <row r="1965"/>
+    <row r="1966"/>
+    <row r="1967"/>
+    <row r="1968"/>
+    <row r="1969"/>
+    <row r="1970"/>
+    <row r="1971"/>
+    <row r="1972"/>
+    <row r="1973"/>
+    <row r="1974"/>
+    <row r="1975"/>
+    <row r="1976"/>
+    <row r="1977"/>
+    <row r="1978"/>
+    <row r="1979"/>
+    <row r="1980"/>
+    <row r="1981"/>
+    <row r="1982"/>
+    <row r="1983"/>
+    <row r="1984"/>
+    <row r="1985"/>
+    <row r="1986"/>
+    <row r="1987"/>
+    <row r="1988"/>
+    <row r="1989"/>
+    <row r="1990"/>
+    <row r="1991"/>
+    <row r="1992"/>
+    <row r="1993"/>
+    <row r="1994"/>
+    <row r="1995"/>
+    <row r="1996"/>
+    <row r="1997"/>
+    <row r="1998"/>
+    <row r="1999"/>
+    <row r="2000"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <autoFilter ref="A1:L1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3129,7 +9414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
